--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_18-08-2026.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_18-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Mannok_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C6782F-D8D4-49E6-8302-9861143EF6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4268F81-967E-4C1F-A7DD-72DA2C89DF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5025" yWindow="1965" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5520" yWindow="2715" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="69">
   <si>
     <t>SKU</t>
   </si>
@@ -161,9 +161,6 @@
   </si>
   <si>
     <t>Mannok Therm PIR 100mm x 2.4m x 1.2m</t>
-  </si>
-  <si>
-    <t>£39.50</t>
   </si>
   <si>
     <t>£39.65</t>
@@ -863,16 +860,16 @@
         <v>46</v>
       </c>
       <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>48</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -883,22 +880,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
         <v>49</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>50</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -909,22 +906,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
         <v>53</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>54</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -935,10 +932,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
         <v>57</v>
-      </c>
-      <c r="B14" t="s">
-        <v>58</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -961,22 +958,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
         <v>59</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>60</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
         <v>61</v>
-      </c>
-      <c r="D15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -987,22 +984,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
         <v>63</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>64</v>
       </c>
-      <c r="C16" t="s">
-        <v>65</v>
-      </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1013,22 +1010,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" t="s">
         <v>66</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>67</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
         <v>68</v>
-      </c>
-      <c r="D17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>69</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>

--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_18-08-2026.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_18-08-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Mannok_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4268F81-967E-4C1F-A7DD-72DA2C89DF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F2F15C-B10A-4111-B474-C66DC9E12645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5520" yWindow="2715" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="70">
   <si>
     <t>SKU</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>£59.45</t>
+  </si>
+  <si>
+    <t>£30.00</t>
   </si>
 </sst>
 </file>
@@ -782,10 +785,10 @@
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
